--- a/Configs/buff_config.xlsx
+++ b/Configs/buff_config.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="85">
   <si>
     <t>id</t>
   </si>
@@ -165,9 +165,6 @@
   </si>
   <si>
     <t>每秒恢复10%攻击力的生命持续10秒</t>
-  </si>
-  <si>
-    <t>0~-1000</t>
   </si>
   <si>
     <t>伤害减免</t>
@@ -1251,6 +1248,9 @@
   <cols>
     <col min="4" max="4" width="33.125" customWidth="1"/>
     <col min="13" max="13" width="12.625" customWidth="1"/>
+    <col min="14" max="14" width="23.75" customWidth="1"/>
+    <col min="15" max="15" width="10.375" customWidth="1"/>
+    <col min="16" max="16" width="11.5" customWidth="1"/>
     <col min="17" max="17" width="26" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2099,11 +2099,9 @@
       <c r="M16" t="s">
         <v>24</v>
       </c>
-      <c r="N16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O16" t="s">
-        <v>24</v>
+      <c r="N16"/>
+      <c r="O16">
+        <v>30001</v>
       </c>
       <c r="P16" t="s">
         <v>24</v>
@@ -2117,40 +2115,40 @@
         <v>5000</v>
       </c>
       <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" t="s">
         <v>47</v>
       </c>
-      <c r="C17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>10000</v>
+      </c>
+      <c r="G17">
+        <v>10000</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="s">
         <v>48</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>10000</v>
-      </c>
-      <c r="G17">
-        <v>10000</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" t="s">
-        <v>24</v>
-      </c>
-      <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17" t="s">
-        <v>49</v>
       </c>
       <c r="N17" t="s">
         <v>24</v>
@@ -2170,13 +2168,13 @@
         <v>6000</v>
       </c>
       <c r="B18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" t="s">
         <v>50</v>
-      </c>
-      <c r="C18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" t="s">
-        <v>51</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2203,7 +2201,7 @@
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N18" t="s">
         <v>24</v>
@@ -2223,13 +2221,13 @@
         <v>7000</v>
       </c>
       <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
         <v>53</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" t="s">
-        <v>54</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2268,7 +2266,7 @@
         <v>24</v>
       </c>
       <c r="Q19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -2277,13 +2275,13 @@
         <v>7001</v>
       </c>
       <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" t="s">
         <v>56</v>
-      </c>
-      <c r="C20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" t="s">
-        <v>57</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -2322,7 +2320,7 @@
         <v>24</v>
       </c>
       <c r="Q20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -2331,13 +2329,13 @@
         <v>7002</v>
       </c>
       <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" t="s">
         <v>59</v>
-      </c>
-      <c r="C21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" t="s">
-        <v>60</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2376,7 +2374,7 @@
         <v>24</v>
       </c>
       <c r="Q21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -2385,13 +2383,13 @@
         <v>7003</v>
       </c>
       <c r="B22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" t="s">
         <v>62</v>
-      </c>
-      <c r="C22" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" t="s">
-        <v>63</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2430,7 +2428,7 @@
         <v>24</v>
       </c>
       <c r="Q22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -2439,13 +2437,13 @@
         <v>7004</v>
       </c>
       <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" t="s">
         <v>65</v>
-      </c>
-      <c r="C23" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" t="s">
-        <v>66</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -2484,7 +2482,7 @@
         <v>24</v>
       </c>
       <c r="Q23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -2493,13 +2491,13 @@
         <v>7005</v>
       </c>
       <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" t="s">
         <v>68</v>
-      </c>
-      <c r="C24" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" t="s">
-        <v>69</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -2538,7 +2536,7 @@
         <v>24</v>
       </c>
       <c r="Q24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -2547,13 +2545,13 @@
         <v>7006</v>
       </c>
       <c r="B25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
         <v>71</v>
-      </c>
-      <c r="C25" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" t="s">
-        <v>72</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -2592,7 +2590,7 @@
         <v>24</v>
       </c>
       <c r="Q25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -2601,13 +2599,13 @@
         <v>7007</v>
       </c>
       <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" t="s">
-        <v>75</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -2646,7 +2644,7 @@
         <v>24</v>
       </c>
       <c r="Q26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -2655,13 +2653,13 @@
         <v>7008</v>
       </c>
       <c r="B27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
         <v>77</v>
-      </c>
-      <c r="C27" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27" t="s">
-        <v>78</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -2700,7 +2698,7 @@
         <v>24</v>
       </c>
       <c r="Q27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -2709,13 +2707,13 @@
         <v>7009</v>
       </c>
       <c r="B28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" t="s">
         <v>80</v>
-      </c>
-      <c r="C28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" t="s">
-        <v>81</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2754,7 +2752,7 @@
         <v>24</v>
       </c>
       <c r="Q28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -2762,13 +2760,13 @@
         <v>8000</v>
       </c>
       <c r="B29" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" t="s">
         <v>83</v>
-      </c>
-      <c r="C29" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" t="s">
-        <v>84</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -2795,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N29" t="s">
         <v>24</v>

--- a/Configs/buff_config.xlsx
+++ b/Configs/buff_config.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="85">
   <si>
     <t>id</t>
   </si>
@@ -2099,7 +2099,6 @@
       <c r="M16" t="s">
         <v>24</v>
       </c>
-      <c r="N16"/>
       <c r="O16">
         <v>30001</v>
       </c>
@@ -2157,9 +2156,6 @@
         <v>24</v>
       </c>
       <c r="P17" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q17" t="s">
         <v>24</v>
       </c>
     </row>

--- a/Configs/buff_config.xlsx
+++ b/Configs/buff_config.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
   <si>
     <t>id</t>
   </si>
@@ -146,6 +146,21 @@
     <t>无法移动10秒</t>
   </si>
   <si>
+    <t>无法移动11秒</t>
+  </si>
+  <si>
+    <t>无法移动12秒</t>
+  </si>
+  <si>
+    <t>无法移动13秒</t>
+  </si>
+  <si>
+    <t>无法移动14秒</t>
+  </si>
+  <si>
+    <t>无法移动15秒</t>
+  </si>
+  <si>
     <t>减速</t>
   </si>
   <si>
@@ -179,10 +194,16 @@
     <t>易伤</t>
   </si>
   <si>
-    <t>受到的伤害增加50%持续3秒</t>
+    <t>受到的伤害增加50%持续5秒</t>
   </si>
   <si>
     <t>109~-5000</t>
+  </si>
+  <si>
+    <t>受到的伤害增加30%持续10秒</t>
+  </si>
+  <si>
+    <t>109~-3000</t>
   </si>
   <si>
     <t>反击 Lv1</t>
@@ -1243,7 +1264,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="33.125" customWidth="1"/>
@@ -1468,7 +1489,7 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5">
-        <f t="shared" ref="A5:A13" si="0">A4+1</f>
+        <f t="shared" ref="A5:A18" si="0">A4+1</f>
         <v>2001</v>
       </c>
       <c r="B5" t="s">
@@ -1954,17 +1975,18 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14">
-        <v>3000</v>
+        <f t="shared" si="0"/>
+        <v>2010</v>
       </c>
       <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" t="s">
         <v>39</v>
       </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" t="s">
-        <v>40</v>
-      </c>
       <c r="E14">
         <v>1</v>
       </c>
@@ -1972,7 +1994,7 @@
         <v>10000</v>
       </c>
       <c r="G14">
-        <v>3000</v>
+        <v>11000</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1990,7 +2012,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="N14" t="s">
         <v>24</v>
@@ -2002,22 +2024,22 @@
         <v>24</v>
       </c>
       <c r="Q14" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15">
-        <f>A14+1</f>
-        <v>3001</v>
+        <f t="shared" si="0"/>
+        <v>2011</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2026,7 +2048,7 @@
         <v>10000</v>
       </c>
       <c r="G15">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2044,7 +2066,7 @@
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="N15" t="s">
         <v>24</v>
@@ -2056,21 +2078,22 @@
         <v>24</v>
       </c>
       <c r="Q15" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16">
-        <v>4000</v>
+        <f t="shared" si="0"/>
+        <v>2012</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
         <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -2079,10 +2102,10 @@
         <v>10000</v>
       </c>
       <c r="G16">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="H16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I16" t="s">
         <v>24</v>
@@ -2091,36 +2114,40 @@
         <v>24</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="s">
         <v>24</v>
       </c>
-      <c r="O16">
-        <v>30001</v>
+      <c r="N16" t="s">
+        <v>24</v>
+      </c>
+      <c r="O16" t="s">
+        <v>24</v>
       </c>
       <c r="P16" t="s">
         <v>24</v>
       </c>
       <c r="Q16" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17">
-        <v>5000</v>
+        <f t="shared" si="0"/>
+        <v>2013</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
         <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2129,7 +2156,7 @@
         <v>10000</v>
       </c>
       <c r="G17">
-        <v>10000</v>
+        <v>14000</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -2141,13 +2168,13 @@
         <v>24</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="N17" t="s">
         <v>24</v>
@@ -2157,20 +2184,24 @@
       </c>
       <c r="P17" t="s">
         <v>24</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:17">
       <c r="A18">
-        <v>6000</v>
+        <f t="shared" si="0"/>
+        <v>2014</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
         <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2179,7 +2210,7 @@
         <v>10000</v>
       </c>
       <c r="G18">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2197,7 +2228,7 @@
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="N18" t="s">
         <v>24</v>
@@ -2209,21 +2240,21 @@
         <v>24</v>
       </c>
       <c r="Q18" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:17">
       <c r="A19">
-        <v>7000</v>
+        <v>3000</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2232,7 +2263,7 @@
         <v>10000</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>3000</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -2244,13 +2275,13 @@
         <v>24</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="N19" t="s">
         <v>24</v>
@@ -2262,22 +2293,22 @@
         <v>24</v>
       </c>
       <c r="Q19" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:17">
       <c r="A20">
-        <f t="shared" ref="A20:A28" si="1">A19+1</f>
-        <v>7001</v>
+        <f>A19+1</f>
+        <v>3001</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>24</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -2286,7 +2317,7 @@
         <v>10000</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>10000</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -2298,13 +2329,13 @@
         <v>24</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="N20" t="s">
         <v>24</v>
@@ -2316,22 +2347,21 @@
         <v>24</v>
       </c>
       <c r="Q20" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:17">
       <c r="A21">
-        <f t="shared" si="1"/>
-        <v>7002</v>
+        <v>4000</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
         <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2340,10 +2370,10 @@
         <v>10000</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>10000</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I21" t="s">
         <v>24</v>
@@ -2360,32 +2390,28 @@
       <c r="M21" t="s">
         <v>24</v>
       </c>
-      <c r="N21" t="s">
-        <v>24</v>
-      </c>
-      <c r="O21" t="s">
-        <v>24</v>
+      <c r="O21">
+        <v>10012</v>
       </c>
       <c r="P21" t="s">
         <v>24</v>
       </c>
       <c r="Q21" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22">
-        <f t="shared" si="1"/>
-        <v>7003</v>
+        <v>5000</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
         <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2394,7 +2420,7 @@
         <v>10000</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>10000</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -2412,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="N22" t="s">
         <v>24</v>
@@ -2422,24 +2448,20 @@
       </c>
       <c r="P22" t="s">
         <v>24</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:17">
       <c r="A23">
-        <f t="shared" si="1"/>
-        <v>7004</v>
+        <v>6000</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
         <v>24</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -2448,7 +2470,7 @@
         <v>10000</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5000</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -2460,13 +2482,13 @@
         <v>24</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="N23" t="s">
         <v>24</v>
@@ -2478,22 +2500,21 @@
         <v>24</v>
       </c>
       <c r="Q23" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:17">
       <c r="A24">
-        <f t="shared" si="1"/>
-        <v>7005</v>
+        <v>6001</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
         <v>24</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -2502,7 +2523,7 @@
         <v>10000</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>10000</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -2514,13 +2535,13 @@
         <v>24</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="N24" t="s">
         <v>24</v>
@@ -2532,22 +2553,21 @@
         <v>24</v>
       </c>
       <c r="Q24" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25">
-        <f t="shared" si="1"/>
-        <v>7006</v>
+        <v>7000</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
         <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -2586,22 +2606,22 @@
         <v>24</v>
       </c>
       <c r="Q25" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:17">
       <c r="A26">
-        <f t="shared" si="1"/>
-        <v>7007</v>
+        <f t="shared" ref="A26:A34" si="1">A25+1</f>
+        <v>7001</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
         <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -2640,22 +2660,22 @@
         <v>24</v>
       </c>
       <c r="Q26" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:17">
       <c r="A27">
         <f t="shared" si="1"/>
-        <v>7008</v>
+        <v>7002</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
         <v>24</v>
       </c>
       <c r="D27" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -2694,22 +2714,22 @@
         <v>24</v>
       </c>
       <c r="Q27" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:17">
       <c r="A28">
         <f t="shared" si="1"/>
-        <v>7009</v>
+        <v>7003</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
         <v>24</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2748,21 +2768,22 @@
         <v>24</v>
       </c>
       <c r="Q28" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:17">
       <c r="A29">
-        <v>8000</v>
+        <f t="shared" si="1"/>
+        <v>7004</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
         <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -2789,18 +2810,341 @@
         <v>0</v>
       </c>
       <c r="M29" t="s">
+        <v>24</v>
+      </c>
+      <c r="N29" t="s">
+        <v>24</v>
+      </c>
+      <c r="O29" t="s">
+        <v>24</v>
+      </c>
+      <c r="P29" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30">
+        <f t="shared" si="1"/>
+        <v>7005</v>
+      </c>
+      <c r="B30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>10000</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" t="s">
+        <v>24</v>
+      </c>
+      <c r="J30" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="s">
+        <v>24</v>
+      </c>
+      <c r="N30" t="s">
+        <v>24</v>
+      </c>
+      <c r="O30" t="s">
+        <v>24</v>
+      </c>
+      <c r="P30" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31">
+        <f t="shared" si="1"/>
+        <v>7006</v>
+      </c>
+      <c r="B31" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>10000</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="s">
+        <v>24</v>
+      </c>
+      <c r="N31" t="s">
+        <v>24</v>
+      </c>
+      <c r="O31" t="s">
+        <v>24</v>
+      </c>
+      <c r="P31" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
+      <c r="A32">
+        <f t="shared" si="1"/>
+        <v>7007</v>
+      </c>
+      <c r="B32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>10000</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" t="s">
+        <v>24</v>
+      </c>
+      <c r="J32" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="s">
+        <v>24</v>
+      </c>
+      <c r="N32" t="s">
+        <v>24</v>
+      </c>
+      <c r="O32" t="s">
+        <v>24</v>
+      </c>
+      <c r="P32" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33">
+        <f t="shared" si="1"/>
+        <v>7008</v>
+      </c>
+      <c r="B33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" t="s">
         <v>84</v>
       </c>
-      <c r="N29" t="s">
-        <v>24</v>
-      </c>
-      <c r="O29" t="s">
-        <v>24</v>
-      </c>
-      <c r="P29" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q29" t="s">
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>10000</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33" t="s">
+        <v>24</v>
+      </c>
+      <c r="J33" t="s">
+        <v>24</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="s">
+        <v>24</v>
+      </c>
+      <c r="N33" t="s">
+        <v>24</v>
+      </c>
+      <c r="O33" t="s">
+        <v>24</v>
+      </c>
+      <c r="P33" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34">
+        <f t="shared" si="1"/>
+        <v>7009</v>
+      </c>
+      <c r="B34" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>10000</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J34" t="s">
+        <v>24</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="s">
+        <v>24</v>
+      </c>
+      <c r="N34" t="s">
+        <v>24</v>
+      </c>
+      <c r="O34" t="s">
+        <v>24</v>
+      </c>
+      <c r="P34" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35">
+        <v>8000</v>
+      </c>
+      <c r="B35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" t="s">
+        <v>90</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>10000</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J35" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="s">
+        <v>91</v>
+      </c>
+      <c r="N35" t="s">
+        <v>24</v>
+      </c>
+      <c r="O35" t="s">
+        <v>24</v>
+      </c>
+      <c r="P35" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q35" t="s">
         <v>24</v>
       </c>
     </row>

--- a/Configs/buff_config.xlsx
+++ b/Configs/buff_config.xlsx
@@ -53,7 +53,7 @@
     <t>jumpTime</t>
   </si>
   <si>
-    <t>persistJson</t>
+    <t>eventEffect</t>
   </si>
   <si>
     <t>position</t>
@@ -1268,6 +1268,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="33.125" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="9" max="9" width="12.625" customWidth="1"/>
     <col min="13" max="13" width="12.625" customWidth="1"/>
     <col min="14" max="14" width="23.75" customWidth="1"/>
     <col min="15" max="15" width="10.375" customWidth="1"/>
@@ -1354,7 +1356,7 @@
         <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
         <v>18</v>
